--- a/forms/trg/Formulir_TRG_aphreg.xlsx
+++ b/forms/trg/Formulir_TRG_aphreg.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B35)</f>
+        <f>COUNTA(Anggota!B5:B36)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F35)</f>
+        <f>COUNTA(Anggota!F5:F36)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,23 +913,35 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Dwi Kesuma Sari</t>
+          <t>Fika Yuliza Purba</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D5" s="12" t="n"/>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
       <c r="E5" s="11" t="n"/>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="12" t="n"/>
-      <c r="J5" s="12" t="n"/>
+      <c r="J5" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-9483-3876</t>
+        </is>
+      </c>
       <c r="K5" s="12" t="n"/>
-      <c r="L5" s="12" t="n"/>
+      <c r="L5" s="11" t="inlineStr">
+        <is>
+          <t>57207245968</t>
+        </is>
+      </c>
       <c r="M5" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -942,12 +954,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Andi Magfira Satya Apada</t>
+          <t>Dwi Kesuma Sari</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="12" t="n"/>
@@ -971,12 +983,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Baso Yusuf</t>
+          <t>Andi Magfira Satya Apada</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="12" t="n"/>
@@ -1000,12 +1012,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Ardiansyah Nurdin</t>
+          <t>Baso Yusuf</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="12" t="n"/>
@@ -1029,12 +1041,12 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Nur Alif Bahmid</t>
+          <t>Muhammad Ardiansyah Nurdin</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="12" t="n"/>
@@ -1058,19 +1070,15 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Muflih Nur</t>
+          <t>Nur Alif Bahmid</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D10" s="11" t="inlineStr">
-        <is>
-          <t>Hasanuddin University</t>
-        </is>
-      </c>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="n"/>
       <c r="E10" s="11" t="n"/>
       <c r="F10" s="12" t="n"/>
       <c r="G10" s="12" t="n"/>
@@ -1091,17 +1099,17 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Erick V. G. Komba</t>
+          <t>Muhammad Muflih Nur</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Senior Lecturer in the Department of Veterinary Medicine and Public Health, Sokoine University</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E11" s="11" t="n"/>
@@ -1109,17 +1117,9 @@
       <c r="G11" s="12" t="n"/>
       <c r="H11" s="12" t="n"/>
       <c r="I11" s="12" t="n"/>
-      <c r="J11" s="11" t="inlineStr">
-        <is>
-          <t>0000-0003-3242-2219</t>
-        </is>
-      </c>
+      <c r="J11" s="12" t="n"/>
       <c r="K11" s="12" t="n"/>
-      <c r="L11" s="11" t="inlineStr">
-        <is>
-          <t>https://www.scopus.com/pages/authors/54883911200</t>
-        </is>
-      </c>
+      <c r="L11" s="12" t="n"/>
       <c r="M11" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1132,17 +1132,17 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Naoki Isobe</t>
+          <t>Erick V. G. Komba</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Hiroshima University</t>
+          <t>Senior Lecturer in the Department of Veterinary Medicine and Public Health, Sokoine University</t>
         </is>
       </c>
       <c r="E12" s="11" t="n"/>
@@ -1152,13 +1152,13 @@
       <c r="I12" s="12" t="n"/>
       <c r="J12" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-9230-6346</t>
+          <t>0000-0003-3242-2219</t>
         </is>
       </c>
       <c r="K12" s="12" t="n"/>
       <c r="L12" s="11" t="inlineStr">
         <is>
-          <t>https://www.scopus.com/pages/authors/24174768400</t>
+          <t>https://www.scopus.com/pages/authors/54883911200</t>
         </is>
       </c>
       <c r="M12" s="11" t="inlineStr">
@@ -1173,17 +1173,17 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Dr. Emely J. Escala</t>
+          <t>Naoki Isobe</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>Capiz State University</t>
+          <t>Hiroshima University</t>
         </is>
       </c>
       <c r="E13" s="11" t="n"/>
@@ -1193,11 +1193,15 @@
       <c r="I13" s="12" t="n"/>
       <c r="J13" s="11" t="inlineStr">
         <is>
-          <t>0000-0003-2666-9901</t>
+          <t>0000-0001-9230-6346</t>
         </is>
       </c>
       <c r="K13" s="12" t="n"/>
-      <c r="L13" s="12" t="n"/>
+      <c r="L13" s="11" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/authors/24174768400</t>
+        </is>
+      </c>
       <c r="M13" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1210,17 +1214,17 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Irwan Ismail</t>
+          <t>Dr. Emely J. Escala</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>Capiz State University</t>
         </is>
       </c>
       <c r="E14" s="11" t="n"/>
@@ -1230,15 +1234,11 @@
       <c r="I14" s="12" t="n"/>
       <c r="J14" s="11" t="inlineStr">
         <is>
-          <t>0009-0006-0391-5806</t>
+          <t>0000-0003-2666-9901</t>
         </is>
       </c>
       <c r="K14" s="12" t="n"/>
-      <c r="L14" s="11" t="inlineStr">
-        <is>
-          <t>58490215600</t>
-        </is>
-      </c>
+      <c r="L14" s="12" t="n"/>
       <c r="M14" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1251,12 +1251,12 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Andi Tri Julyana Eka Astuty</t>
+          <t>Irwan Ismail</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
@@ -1271,13 +1271,13 @@
       <c r="I15" s="12" t="n"/>
       <c r="J15" s="11" t="inlineStr">
         <is>
-          <t>0009-0009-2814-2813</t>
+          <t>0009-0006-0391-5806</t>
         </is>
       </c>
       <c r="K15" s="12" t="n"/>
       <c r="L15" s="11" t="inlineStr">
         <is>
-          <t>https://www.scopus.com/pages/authors/57218700940</t>
+          <t>58490215600</t>
         </is>
       </c>
       <c r="M15" s="11" t="inlineStr">
@@ -1292,17 +1292,17 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>lphan Augusta Kajang</t>
+          <t>Andi Tri Julyana Eka Astuty</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>Universitas Hasanuddin</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E16" s="11" t="n"/>
@@ -1310,9 +1310,17 @@
       <c r="G16" s="12" t="n"/>
       <c r="H16" s="12" t="n"/>
       <c r="I16" s="12" t="n"/>
-      <c r="J16" s="12" t="n"/>
+      <c r="J16" s="11" t="inlineStr">
+        <is>
+          <t>0009-0009-2814-2813</t>
+        </is>
+      </c>
       <c r="K16" s="12" t="n"/>
-      <c r="L16" s="12" t="n"/>
+      <c r="L16" s="11" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/authors/57218700940</t>
+        </is>
+      </c>
       <c r="M16" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1325,17 +1333,17 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Kadek Dian Krisna Putri K</t>
+          <t>lphan Augusta Kajang</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>Universitas Hasanuddin</t>
         </is>
       </c>
       <c r="E17" s="11" t="n"/>
@@ -1343,11 +1351,7 @@
       <c r="G17" s="12" t="n"/>
       <c r="H17" s="12" t="n"/>
       <c r="I17" s="12" t="n"/>
-      <c r="J17" s="11" t="inlineStr">
-        <is>
-          <t>0009-0009-6604-3859</t>
-        </is>
-      </c>
+      <c r="J17" s="12" t="n"/>
       <c r="K17" s="12" t="n"/>
       <c r="L17" s="12" t="n"/>
       <c r="M17" s="11" t="inlineStr">
@@ -1362,12 +1366,12 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Zainal Abidin Kholilullah</t>
+          <t>Kadek Dian Krisna Putri K</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
@@ -1382,7 +1386,7 @@
       <c r="I18" s="12" t="n"/>
       <c r="J18" s="11" t="inlineStr">
         <is>
-          <t>0009-0000-3859-122X</t>
+          <t>0009-0009-6604-3859</t>
         </is>
       </c>
       <c r="K18" s="12" t="n"/>
@@ -1399,12 +1403,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>Rasdiyanah</t>
+          <t>Zainal Abidin Kholilullah</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
@@ -1419,7 +1423,7 @@
       <c r="I19" s="12" t="n"/>
       <c r="J19" s="11" t="inlineStr">
         <is>
-          <t>0009-0005-1645-1812</t>
+          <t>0009-0000-3859-122X</t>
         </is>
       </c>
       <c r="K19" s="12" t="n"/>
@@ -1436,12 +1440,12 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>Anjani Marisa Kartikasari</t>
+          <t>Rasdiyanah</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
@@ -1456,7 +1460,7 @@
       <c r="I20" s="12" t="n"/>
       <c r="J20" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-8030-9010</t>
+          <t>0009-0005-1645-1812</t>
         </is>
       </c>
       <c r="K20" s="12" t="n"/>
@@ -1473,12 +1477,12 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>Amelia Ramadhani Anshar</t>
+          <t>Anjani Marisa Kartikasari</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
@@ -1493,7 +1497,7 @@
       <c r="I21" s="12" t="n"/>
       <c r="J21" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-5169-8013</t>
+          <t>0000-0002-8030-9010</t>
         </is>
       </c>
       <c r="K21" s="12" t="n"/>
@@ -1510,12 +1514,12 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>Subaedy Yusuf</t>
+          <t>Amelia Ramadhani Anshar</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
@@ -1528,7 +1532,11 @@
       <c r="G22" s="12" t="n"/>
       <c r="H22" s="12" t="n"/>
       <c r="I22" s="12" t="n"/>
-      <c r="J22" s="12" t="n"/>
+      <c r="J22" s="11" t="inlineStr">
+        <is>
+          <t>0000-0001-5169-8013</t>
+        </is>
+      </c>
       <c r="K22" s="12" t="n"/>
       <c r="L22" s="12" t="n"/>
       <c r="M22" s="11" t="inlineStr">
@@ -1543,17 +1551,17 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>Ahmad Muchlis</t>
+          <t>Subaedy Yusuf</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>University of Bosowa</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E23" s="11" t="n"/>
@@ -1561,11 +1569,7 @@
       <c r="G23" s="12" t="n"/>
       <c r="H23" s="12" t="n"/>
       <c r="I23" s="12" t="n"/>
-      <c r="J23" s="11" t="inlineStr">
-        <is>
-          <t>0000-0002-6645-8036</t>
-        </is>
-      </c>
+      <c r="J23" s="12" t="n"/>
       <c r="K23" s="12" t="n"/>
       <c r="L23" s="12" t="n"/>
       <c r="M23" s="11" t="inlineStr">
@@ -1578,18 +1582,42 @@
       <c r="A24" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="12" t="n"/>
-      <c r="C24" s="12" t="n"/>
-      <c r="D24" s="12" t="n"/>
-      <c r="E24" s="11" t="n"/>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>Ahmad Muchlis</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>University of Bosowa</t>
+        </is>
+      </c>
+      <c r="E24" s="11" t="inlineStr">
+        <is>
+          <t>We are a multidisciplinary team dedicated to advancing the science of infectious animal disease dynamics to address global challenges such as zoonotic disease transmission, animal health, and sustainable disease control. Through innovative research and practical applications, we improve understanding of how diseases spread, their impact on animal populations, and their interactions with human health.</t>
+        </is>
+      </c>
       <c r="F24" s="12" t="n"/>
       <c r="G24" s="12" t="n"/>
       <c r="H24" s="12" t="n"/>
       <c r="I24" s="12" t="n"/>
-      <c r="J24" s="12" t="n"/>
+      <c r="J24" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-6645-8036</t>
+        </is>
+      </c>
       <c r="K24" s="12" t="n"/>
       <c r="L24" s="12" t="n"/>
-      <c r="M24" s="12" t="n"/>
+      <c r="M24" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
@@ -1778,15 +1806,32 @@
       <c r="L35" s="12" t="n"/>
       <c r="M35" s="12" t="n"/>
     </row>
+    <row r="36">
+      <c r="A36" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="12" t="n"/>
+      <c r="C36" s="12" t="n"/>
+      <c r="D36" s="12" t="n"/>
+      <c r="E36" s="11" t="n"/>
+      <c r="F36" s="12" t="n"/>
+      <c r="G36" s="12" t="n"/>
+      <c r="H36" s="12" t="n"/>
+      <c r="I36" s="12" t="n"/>
+      <c r="J36" s="12" t="n"/>
+      <c r="K36" s="12" t="n"/>
+      <c r="L36" s="12" t="n"/>
+      <c r="M36" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
